--- a/src/output/Pad/excels/Etiket/ETIKETLER_TEK_JSON_1.xlsx
+++ b/src/output/Pad/excels/Etiket/ETIKETLER_TEK_JSON_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\URETIM9\Desktop\Projects\API_SCRAPE\src\output\Pad\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\URETIM9\Desktop\Projects\API_SCRAPE\src\output\Pad\excels\Etiket\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{686C27B8-3760-4B8C-B47C-BDAEE13BB4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA4D507-5EE9-403B-BB78-51321D17FD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1068" yWindow="2100" windowWidth="20532" windowHeight="10140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Etiketler" sheetId="1" r:id="rId1"/>
@@ -7385,15 +7385,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFEB9C"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -7415,12 +7407,10 @@
       </fill>
     </dxf>
     <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB9C"/>
+          <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -7759,7 +7749,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C863"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
@@ -7779,7 +7768,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -7790,7 +7779,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -7801,7 +7790,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -7812,7 +7801,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -7823,7 +7812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -7834,7 +7823,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -7845,7 +7834,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -7856,7 +7845,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -7867,7 +7856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -7878,7 +7867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -7889,7 +7878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -7900,7 +7889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -7911,7 +7900,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -7922,7 +7911,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -7933,7 +7922,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -7944,7 +7933,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -7955,7 +7944,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -7966,7 +7955,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -7977,7 +7966,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>54</v>
       </c>
@@ -7999,7 +7988,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>60</v>
       </c>
@@ -8010,7 +7999,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -8021,7 +8010,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>66</v>
       </c>
@@ -8032,7 +8021,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -8043,7 +8032,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>72</v>
       </c>
@@ -8054,7 +8043,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -8065,7 +8054,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>78</v>
       </c>
@@ -8076,7 +8065,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -8098,7 +8087,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -8109,7 +8098,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>87</v>
       </c>
@@ -8120,7 +8109,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>90</v>
       </c>
@@ -8131,7 +8120,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>93</v>
       </c>
@@ -8142,7 +8131,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>96</v>
       </c>
@@ -8153,7 +8142,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>96</v>
       </c>
@@ -8164,7 +8153,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>101</v>
       </c>
@@ -8175,7 +8164,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>104</v>
       </c>
@@ -8186,7 +8175,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>107</v>
       </c>
@@ -8197,7 +8186,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>110</v>
       </c>
@@ -8208,7 +8197,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>113</v>
       </c>
@@ -8219,7 +8208,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>116</v>
       </c>
@@ -8230,7 +8219,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>119</v>
       </c>
@@ -8241,7 +8230,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>122</v>
       </c>
@@ -8252,7 +8241,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>125</v>
       </c>
@@ -8263,7 +8252,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>128</v>
       </c>
@@ -8274,7 +8263,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>131</v>
       </c>
@@ -8285,7 +8274,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>134</v>
       </c>
@@ -8296,7 +8285,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>137</v>
       </c>
@@ -8307,7 +8296,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>140</v>
       </c>
@@ -8318,7 +8307,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>143</v>
       </c>
@@ -8329,7 +8318,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>146</v>
       </c>
@@ -8340,7 +8329,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>149</v>
       </c>
@@ -8351,7 +8340,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>152</v>
       </c>
@@ -8362,7 +8351,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>155</v>
       </c>
@@ -8373,7 +8362,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>158</v>
       </c>
@@ -8384,7 +8373,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>161</v>
       </c>
@@ -8395,7 +8384,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>164</v>
       </c>
@@ -8406,7 +8395,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>167</v>
       </c>
@@ -8417,7 +8406,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>167</v>
       </c>
@@ -8428,7 +8417,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>167</v>
       </c>
@@ -8439,7 +8428,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>173</v>
       </c>
@@ -8450,7 +8439,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>176</v>
       </c>
@@ -8461,7 +8450,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>179</v>
       </c>
@@ -8472,7 +8461,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>182</v>
       </c>
@@ -8483,7 +8472,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>184</v>
       </c>
@@ -8494,7 +8483,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>187</v>
       </c>
@@ -8505,7 +8494,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>190</v>
       </c>
@@ -8516,7 +8505,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>193</v>
       </c>
@@ -8527,7 +8516,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>196</v>
       </c>
@@ -8538,7 +8527,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>199</v>
       </c>
@@ -8549,7 +8538,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>202</v>
       </c>
@@ -8560,7 +8549,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>205</v>
       </c>
@@ -8571,7 +8560,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>208</v>
       </c>
@@ -8582,7 +8571,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>211</v>
       </c>
@@ -8593,7 +8582,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>214</v>
       </c>
@@ -8604,7 +8593,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>214</v>
       </c>
@@ -8615,7 +8604,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>219</v>
       </c>
@@ -8626,7 +8615,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>222</v>
       </c>
@@ -8637,7 +8626,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>225</v>
       </c>
@@ -8648,7 +8637,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>228</v>
       </c>
@@ -8659,7 +8648,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>231</v>
       </c>
@@ -8670,7 +8659,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>234</v>
       </c>
@@ -8681,7 +8670,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>237</v>
       </c>
@@ -8692,7 +8681,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>240</v>
       </c>
@@ -8703,7 +8692,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>243</v>
       </c>
@@ -8714,7 +8703,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>246</v>
       </c>
@@ -8725,7 +8714,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>249</v>
       </c>
@@ -8736,7 +8725,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>252</v>
       </c>
@@ -8747,7 +8736,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>255</v>
       </c>
@@ -8758,7 +8747,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>258</v>
       </c>
@@ -8769,7 +8758,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>261</v>
       </c>
@@ -8780,7 +8769,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>261</v>
       </c>
@@ -8791,7 +8780,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>266</v>
       </c>
@@ -8802,7 +8791,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>269</v>
       </c>
@@ -8813,7 +8802,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>272</v>
       </c>
@@ -8824,7 +8813,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>275</v>
       </c>
@@ -8835,7 +8824,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>278</v>
       </c>
@@ -8846,7 +8835,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>281</v>
       </c>
@@ -8857,7 +8846,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>284</v>
       </c>
@@ -8868,7 +8857,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>287</v>
       </c>
@@ -8879,7 +8868,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>289</v>
       </c>
@@ -8890,7 +8879,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>291</v>
       </c>
@@ -8901,7 +8890,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>291</v>
       </c>
@@ -8912,7 +8901,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>295</v>
       </c>
@@ -8923,7 +8912,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>298</v>
       </c>
@@ -8934,7 +8923,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>301</v>
       </c>
@@ -8945,7 +8934,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>301</v>
       </c>
@@ -8956,7 +8945,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>306</v>
       </c>
@@ -8967,7 +8956,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>306</v>
       </c>
@@ -8978,7 +8967,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>311</v>
       </c>
@@ -8989,7 +8978,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>314</v>
       </c>
@@ -9000,7 +8989,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>317</v>
       </c>
@@ -9011,7 +9000,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>320</v>
       </c>
@@ -9022,7 +9011,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>320</v>
       </c>
@@ -9033,7 +9022,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>324</v>
       </c>
@@ -9044,7 +9033,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>327</v>
       </c>
@@ -9055,7 +9044,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>330</v>
       </c>
@@ -9066,7 +9055,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>333</v>
       </c>
@@ -9077,7 +9066,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>336</v>
       </c>
@@ -9088,7 +9077,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>339</v>
       </c>
@@ -9099,7 +9088,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>339</v>
       </c>
@@ -9110,7 +9099,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>344</v>
       </c>
@@ -9121,7 +9110,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>347</v>
       </c>
@@ -9132,7 +9121,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>347</v>
       </c>
@@ -9143,7 +9132,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>351</v>
       </c>
@@ -9154,7 +9143,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>354</v>
       </c>
@@ -9165,7 +9154,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>354</v>
       </c>
@@ -9176,7 +9165,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>354</v>
       </c>
@@ -9187,7 +9176,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>360</v>
       </c>
@@ -9198,7 +9187,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>363</v>
       </c>
@@ -9209,7 +9198,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>366</v>
       </c>
@@ -9220,7 +9209,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>369</v>
       </c>
@@ -9231,7 +9220,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>372</v>
       </c>
@@ -9242,7 +9231,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>375</v>
       </c>
@@ -9253,7 +9242,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>378</v>
       </c>
@@ -9264,7 +9253,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>381</v>
       </c>
@@ -9275,7 +9264,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>384</v>
       </c>
@@ -9286,7 +9275,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>387</v>
       </c>
@@ -9297,7 +9286,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>390</v>
       </c>
@@ -9308,7 +9297,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>393</v>
       </c>
@@ -9319,7 +9308,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>396</v>
       </c>
@@ -9330,7 +9319,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>399</v>
       </c>
@@ -9341,7 +9330,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>402</v>
       </c>
@@ -9352,7 +9341,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>402</v>
       </c>
@@ -9363,7 +9352,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>406</v>
       </c>
@@ -9374,7 +9363,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>409</v>
       </c>
@@ -9385,7 +9374,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>409</v>
       </c>
@@ -9396,7 +9385,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>413</v>
       </c>
@@ -9407,7 +9396,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>416</v>
       </c>
@@ -9418,7 +9407,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>416</v>
       </c>
@@ -9429,7 +9418,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>420</v>
       </c>
@@ -9440,7 +9429,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>422</v>
       </c>
@@ -9451,7 +9440,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>425</v>
       </c>
@@ -9462,7 +9451,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>425</v>
       </c>
@@ -9473,7 +9462,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>425</v>
       </c>
@@ -9484,7 +9473,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>432</v>
       </c>
@@ -9495,7 +9484,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>435</v>
       </c>
@@ -9506,7 +9495,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>438</v>
       </c>
@@ -9517,7 +9506,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>438</v>
       </c>
@@ -9528,7 +9517,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>442</v>
       </c>
@@ -9539,7 +9528,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>442</v>
       </c>
@@ -9550,7 +9539,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>446</v>
       </c>
@@ -9561,7 +9550,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>449</v>
       </c>
@@ -9572,7 +9561,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>452</v>
       </c>
@@ -9583,7 +9572,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>455</v>
       </c>
@@ -9594,7 +9583,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>458</v>
       </c>
@@ -9605,7 +9594,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>461</v>
       </c>
@@ -9616,7 +9605,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>461</v>
       </c>
@@ -9627,7 +9616,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>465</v>
       </c>
@@ -9638,7 +9627,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>465</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>469</v>
       </c>
@@ -9660,7 +9649,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>472</v>
       </c>
@@ -9671,7 +9660,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>472</v>
       </c>
@@ -9682,7 +9671,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>476</v>
       </c>
@@ -9693,7 +9682,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>479</v>
       </c>
@@ -9704,7 +9693,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>482</v>
       </c>
@@ -9715,7 +9704,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>485</v>
       </c>
@@ -9726,7 +9715,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>488</v>
       </c>
@@ -9737,7 +9726,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>491</v>
       </c>
@@ -9748,7 +9737,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>494</v>
       </c>
@@ -9759,7 +9748,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>496</v>
       </c>
@@ -9770,7 +9759,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>499</v>
       </c>
@@ -9781,7 +9770,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>499</v>
       </c>
@@ -9792,7 +9781,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>503</v>
       </c>
@@ -9803,7 +9792,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>506</v>
       </c>
@@ -9814,7 +9803,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>506</v>
       </c>
@@ -9825,7 +9814,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>511</v>
       </c>
@@ -9836,7 +9825,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>511</v>
       </c>
@@ -9847,7 +9836,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>515</v>
       </c>
@@ -9858,7 +9847,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>518</v>
       </c>
@@ -9869,7 +9858,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>520</v>
       </c>
@@ -9880,7 +9869,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>520</v>
       </c>
@@ -9891,7 +9880,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>524</v>
       </c>
@@ -9902,7 +9891,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>527</v>
       </c>
@@ -9913,7 +9902,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>530</v>
       </c>
@@ -9924,7 +9913,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>533</v>
       </c>
@@ -9935,7 +9924,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>536</v>
       </c>
@@ -9946,7 +9935,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>539</v>
       </c>
@@ -9957,7 +9946,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>542</v>
       </c>
@@ -9968,7 +9957,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>545</v>
       </c>
@@ -9979,7 +9968,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>548</v>
       </c>
@@ -9990,7 +9979,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>551</v>
       </c>
@@ -10001,7 +9990,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>553</v>
       </c>
@@ -10012,7 +10001,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>556</v>
       </c>
@@ -10023,7 +10012,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>558</v>
       </c>
@@ -10034,7 +10023,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>561</v>
       </c>
@@ -10045,7 +10034,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>564</v>
       </c>
@@ -10056,7 +10045,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>567</v>
       </c>
@@ -10067,7 +10056,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>569</v>
       </c>
@@ -10078,7 +10067,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>572</v>
       </c>
@@ -10089,7 +10078,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>575</v>
       </c>
@@ -10100,7 +10089,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>575</v>
       </c>
@@ -10111,7 +10100,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>578</v>
       </c>
@@ -10122,7 +10111,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>578</v>
       </c>
@@ -10133,7 +10122,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>582</v>
       </c>
@@ -10144,7 +10133,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>585</v>
       </c>
@@ -10155,7 +10144,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>588</v>
       </c>
@@ -10166,7 +10155,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>590</v>
       </c>
@@ -10188,7 +10177,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>596</v>
       </c>
@@ -10199,7 +10188,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>599</v>
       </c>
@@ -10210,7 +10199,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>602</v>
       </c>
@@ -10221,7 +10210,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>602</v>
       </c>
@@ -10232,7 +10221,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>606</v>
       </c>
@@ -10243,7 +10232,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>608</v>
       </c>
@@ -10254,7 +10243,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>611</v>
       </c>
@@ -10265,7 +10254,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>614</v>
       </c>
@@ -10276,7 +10265,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>614</v>
       </c>
@@ -10287,7 +10276,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>618</v>
       </c>
@@ -10298,7 +10287,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>621</v>
       </c>
@@ -10309,7 +10298,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>621</v>
       </c>
@@ -10320,7 +10309,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>626</v>
       </c>
@@ -10331,7 +10320,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>629</v>
       </c>
@@ -10342,7 +10331,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>632</v>
       </c>
@@ -10353,7 +10342,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>635</v>
       </c>
@@ -10364,7 +10353,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>638</v>
       </c>
@@ -10375,7 +10364,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>638</v>
       </c>
@@ -10386,7 +10375,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>642</v>
       </c>
@@ -10397,7 +10386,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>642</v>
       </c>
@@ -10408,7 +10397,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>646</v>
       </c>
@@ -10419,7 +10408,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>646</v>
       </c>
@@ -10430,7 +10419,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>651</v>
       </c>
@@ -10441,7 +10430,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>654</v>
       </c>
@@ -10452,7 +10441,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>654</v>
       </c>
@@ -10463,7 +10452,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>654</v>
       </c>
@@ -10474,7 +10463,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>660</v>
       </c>
@@ -10485,7 +10474,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>663</v>
       </c>
@@ -10496,7 +10485,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>666</v>
       </c>
@@ -10507,7 +10496,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>669</v>
       </c>
@@ -10518,7 +10507,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>669</v>
       </c>
@@ -10529,7 +10518,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>674</v>
       </c>
@@ -10540,7 +10529,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>674</v>
       </c>
@@ -10551,7 +10540,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>678</v>
       </c>
@@ -10562,7 +10551,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>680</v>
       </c>
@@ -10573,7 +10562,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>682</v>
       </c>
@@ -10584,7 +10573,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>684</v>
       </c>
@@ -10595,7 +10584,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>687</v>
       </c>
@@ -10606,7 +10595,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>690</v>
       </c>
@@ -10617,7 +10606,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>692</v>
       </c>
@@ -10628,7 +10617,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>695</v>
       </c>
@@ -10639,7 +10628,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>695</v>
       </c>
@@ -10650,7 +10639,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>699</v>
       </c>
@@ -10661,7 +10650,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>702</v>
       </c>
@@ -10672,7 +10661,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>705</v>
       </c>
@@ -10683,7 +10672,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>705</v>
       </c>
@@ -10694,7 +10683,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>710</v>
       </c>
@@ -10705,7 +10694,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>713</v>
       </c>
@@ -10716,7 +10705,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>716</v>
       </c>
@@ -10727,7 +10716,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>719</v>
       </c>
@@ -10738,7 +10727,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>722</v>
       </c>
@@ -10749,7 +10738,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>725</v>
       </c>
@@ -10760,7 +10749,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>728</v>
       </c>
@@ -10771,7 +10760,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>731</v>
       </c>
@@ -10793,7 +10782,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>733</v>
       </c>
@@ -10815,7 +10804,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>738</v>
       </c>
@@ -10826,7 +10815,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>738</v>
       </c>
@@ -10837,7 +10826,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>742</v>
       </c>
@@ -10848,7 +10837,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>742</v>
       </c>
@@ -10859,7 +10848,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>747</v>
       </c>
@@ -10870,7 +10859,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>750</v>
       </c>
@@ -10881,7 +10870,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>753</v>
       </c>
@@ -10892,7 +10881,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>756</v>
       </c>
@@ -10903,7 +10892,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>759</v>
       </c>
@@ -10914,7 +10903,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>762</v>
       </c>
@@ -10925,7 +10914,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>764</v>
       </c>
@@ -10936,7 +10925,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>767</v>
       </c>
@@ -10947,7 +10936,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>770</v>
       </c>
@@ -10958,7 +10947,7 @@
         <v>772</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>773</v>
       </c>
@@ -10969,7 +10958,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>773</v>
       </c>
@@ -10980,7 +10969,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>777</v>
       </c>
@@ -10991,7 +10980,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>777</v>
       </c>
@@ -11002,7 +10991,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>777</v>
       </c>
@@ -11013,7 +11002,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>783</v>
       </c>
@@ -11024,7 +11013,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>786</v>
       </c>
@@ -11035,7 +11024,7 @@
         <v>788</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>789</v>
       </c>
@@ -11046,7 +11035,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>791</v>
       </c>
@@ -11057,7 +11046,7 @@
         <v>793</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>794</v>
       </c>
@@ -11068,7 +11057,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>794</v>
       </c>
@@ -11079,7 +11068,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>799</v>
       </c>
@@ -11090,7 +11079,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>801</v>
       </c>
@@ -11101,7 +11090,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>801</v>
       </c>
@@ -11112,7 +11101,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>805</v>
       </c>
@@ -11123,7 +11112,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>808</v>
       </c>
@@ -11134,7 +11123,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>811</v>
       </c>
@@ -11145,7 +11134,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>813</v>
       </c>
@@ -11156,7 +11145,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>816</v>
       </c>
@@ -11167,7 +11156,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>816</v>
       </c>
@@ -11178,7 +11167,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>821</v>
       </c>
@@ -11189,7 +11178,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>824</v>
       </c>
@@ -11200,7 +11189,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>827</v>
       </c>
@@ -11211,7 +11200,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>830</v>
       </c>
@@ -11222,7 +11211,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>833</v>
       </c>
@@ -11233,7 +11222,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>836</v>
       </c>
@@ -11244,7 +11233,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>839</v>
       </c>
@@ -11255,7 +11244,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="318" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>842</v>
       </c>
@@ -11266,7 +11255,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>842</v>
       </c>
@@ -11277,7 +11266,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="320" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>847</v>
       </c>
@@ -11288,7 +11277,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="321" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>850</v>
       </c>
@@ -11299,7 +11288,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="322" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>853</v>
       </c>
@@ -11310,7 +11299,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>856</v>
       </c>
@@ -11321,7 +11310,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>856</v>
       </c>
@@ -11343,7 +11332,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="326" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>862</v>
       </c>
@@ -11354,7 +11343,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="327" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>865</v>
       </c>
@@ -11365,7 +11354,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="328" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>865</v>
       </c>
@@ -11376,7 +11365,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="329" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>869</v>
       </c>
@@ -11387,7 +11376,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="330" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>869</v>
       </c>
@@ -11398,7 +11387,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>873</v>
       </c>
@@ -11409,7 +11398,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="332" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>876</v>
       </c>
@@ -11420,7 +11409,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>879</v>
       </c>
@@ -11431,7 +11420,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="334" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>882</v>
       </c>
@@ -11442,7 +11431,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="335" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>885</v>
       </c>
@@ -11453,7 +11442,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="336" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>885</v>
       </c>
@@ -11464,7 +11453,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="337" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>889</v>
       </c>
@@ -11475,7 +11464,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="338" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>889</v>
       </c>
@@ -11486,7 +11475,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="339" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>893</v>
       </c>
@@ -11497,7 +11486,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="340" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>896</v>
       </c>
@@ -11508,7 +11497,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="341" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>896</v>
       </c>
@@ -11519,7 +11508,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="342" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>900</v>
       </c>
@@ -11530,7 +11519,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="343" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>903</v>
       </c>
@@ -11541,7 +11530,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="344" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>906</v>
       </c>
@@ -11552,7 +11541,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>906</v>
       </c>
@@ -11563,7 +11552,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="346" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>910</v>
       </c>
@@ -11574,7 +11563,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>913</v>
       </c>
@@ -11585,7 +11574,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="348" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>915</v>
       </c>
@@ -11596,7 +11585,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="349" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>918</v>
       </c>
@@ -11607,7 +11596,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>918</v>
       </c>
@@ -11618,7 +11607,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="351" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>922</v>
       </c>
@@ -11629,7 +11618,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="352" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>925</v>
       </c>
@@ -11640,7 +11629,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>925</v>
       </c>
@@ -11651,7 +11640,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="354" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>930</v>
       </c>
@@ -11662,7 +11651,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>933</v>
       </c>
@@ -11673,7 +11662,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="356" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>936</v>
       </c>
@@ -11684,7 +11673,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>938</v>
       </c>
@@ -11695,7 +11684,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>941</v>
       </c>
@@ -11706,7 +11695,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="359" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>944</v>
       </c>
@@ -11717,7 +11706,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="360" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>947</v>
       </c>
@@ -11728,7 +11717,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="361" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>950</v>
       </c>
@@ -11739,7 +11728,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="362" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>950</v>
       </c>
@@ -11750,7 +11739,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="363" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>954</v>
       </c>
@@ -11761,7 +11750,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="364" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>954</v>
       </c>
@@ -11772,7 +11761,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="365" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>957</v>
       </c>
@@ -11783,7 +11772,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="366" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>957</v>
       </c>
@@ -11794,7 +11783,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="367" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>962</v>
       </c>
@@ -11805,7 +11794,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>962</v>
       </c>
@@ -11816,7 +11805,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="369" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>962</v>
       </c>
@@ -11827,7 +11816,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>969</v>
       </c>
@@ -11838,7 +11827,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>969</v>
       </c>
@@ -11849,7 +11838,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="372" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>974</v>
       </c>
@@ -11860,7 +11849,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="373" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>977</v>
       </c>
@@ -11871,7 +11860,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>980</v>
       </c>
@@ -11882,7 +11871,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>980</v>
       </c>
@@ -11893,7 +11882,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="376" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>984</v>
       </c>
@@ -11904,7 +11893,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>984</v>
       </c>
@@ -11937,7 +11926,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="380" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>992</v>
       </c>
@@ -11948,7 +11937,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="381" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>995</v>
       </c>
@@ -11959,7 +11948,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>998</v>
       </c>
@@ -11970,7 +11959,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="383" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>1001</v>
       </c>
@@ -11981,7 +11970,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>1001</v>
       </c>
@@ -11992,7 +11981,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="385" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>1005</v>
       </c>
@@ -12003,7 +11992,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>1005</v>
       </c>
@@ -12014,7 +12003,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="387" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>1010</v>
       </c>
@@ -12025,7 +12014,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="388" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>1013</v>
       </c>
@@ -12036,7 +12025,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>1016</v>
       </c>
@@ -12047,7 +12036,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>1016</v>
       </c>
@@ -12058,7 +12047,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="391" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>1020</v>
       </c>
@@ -12069,7 +12058,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="392" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>1020</v>
       </c>
@@ -12080,7 +12069,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>1024</v>
       </c>
@@ -12091,7 +12080,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="394" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>1027</v>
       </c>
@@ -12113,7 +12102,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="396" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>1031</v>
       </c>
@@ -12135,7 +12124,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="398" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>1031</v>
       </c>
@@ -12146,7 +12135,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>1031</v>
       </c>
@@ -12157,7 +12146,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>1037</v>
       </c>
@@ -12168,7 +12157,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="401" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>1039</v>
       </c>
@@ -12179,7 +12168,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>1039</v>
       </c>
@@ -12190,7 +12179,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>1039</v>
       </c>
@@ -12201,7 +12190,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>1045</v>
       </c>
@@ -12212,7 +12201,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="405" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>1048</v>
       </c>
@@ -12223,7 +12212,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>1051</v>
       </c>
@@ -12234,7 +12223,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>1054</v>
       </c>
@@ -12245,7 +12234,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="408" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>1057</v>
       </c>
@@ -12256,7 +12245,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="409" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>1057</v>
       </c>
@@ -12267,7 +12256,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="410" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>1062</v>
       </c>
@@ -12289,7 +12278,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1065</v>
       </c>
@@ -12300,7 +12289,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1065</v>
       </c>
@@ -12322,7 +12311,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1070</v>
       </c>
@@ -12333,7 +12322,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="416" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1072</v>
       </c>
@@ -12344,7 +12333,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="417" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1075</v>
       </c>
@@ -12366,7 +12355,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="419" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1077</v>
       </c>
@@ -12377,7 +12366,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="420" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1077</v>
       </c>
@@ -12399,7 +12388,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1081</v>
       </c>
@@ -12410,7 +12399,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="423" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1083</v>
       </c>
@@ -12421,7 +12410,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="424" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1086</v>
       </c>
@@ -12432,7 +12421,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="425" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1086</v>
       </c>
@@ -12443,7 +12432,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="426" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1090</v>
       </c>
@@ -12454,7 +12443,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="427" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1090</v>
       </c>
@@ -12465,7 +12454,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="428" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1094</v>
       </c>
@@ -12476,7 +12465,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="429" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1097</v>
       </c>
@@ -12487,7 +12476,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="430" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1100</v>
       </c>
@@ -12498,7 +12487,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1103</v>
       </c>
@@ -12509,7 +12498,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="432" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1105</v>
       </c>
@@ -12520,7 +12509,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="433" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1105</v>
       </c>
@@ -12531,7 +12520,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="434" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1109</v>
       </c>
@@ -12542,7 +12531,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="435" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1109</v>
       </c>
@@ -12553,7 +12542,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="436" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1109</v>
       </c>
@@ -12564,7 +12553,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="437" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1109</v>
       </c>
@@ -12575,7 +12564,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="438" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1116</v>
       </c>
@@ -12586,7 +12575,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="439" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1116</v>
       </c>
@@ -12597,7 +12586,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="440" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1120</v>
       </c>
@@ -12608,7 +12597,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="441" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1123</v>
       </c>
@@ -12619,7 +12608,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="442" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1126</v>
       </c>
@@ -12630,7 +12619,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="443" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1128</v>
       </c>
@@ -12641,7 +12630,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1131</v>
       </c>
@@ -12652,7 +12641,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="445" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1134</v>
       </c>
@@ -12663,7 +12652,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="446" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1134</v>
       </c>
@@ -12674,7 +12663,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1134</v>
       </c>
@@ -12685,7 +12674,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="448" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1140</v>
       </c>
@@ -12696,7 +12685,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1143</v>
       </c>
@@ -12707,7 +12696,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1146</v>
       </c>
@@ -12718,7 +12707,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1146</v>
       </c>
@@ -12729,7 +12718,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="452" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1150</v>
       </c>
@@ -12740,7 +12729,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="453" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1153</v>
       </c>
@@ -12751,7 +12740,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="454" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1153</v>
       </c>
@@ -12762,7 +12751,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="455" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1156</v>
       </c>
@@ -12773,7 +12762,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="456" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1156</v>
       </c>
@@ -12784,7 +12773,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="457" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1161</v>
       </c>
@@ -12795,7 +12784,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="458" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>1164</v>
       </c>
@@ -12806,7 +12795,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="459" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1164</v>
       </c>
@@ -12817,7 +12806,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="460" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1168</v>
       </c>
@@ -12828,7 +12817,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1171</v>
       </c>
@@ -12839,7 +12828,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1171</v>
       </c>
@@ -12850,7 +12839,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="463" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1176</v>
       </c>
@@ -12861,7 +12850,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="464" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1176</v>
       </c>
@@ -12872,7 +12861,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1176</v>
       </c>
@@ -12883,7 +12872,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="466" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1182</v>
       </c>
@@ -12894,7 +12883,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="467" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1185</v>
       </c>
@@ -12905,7 +12894,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="468" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1188</v>
       </c>
@@ -12916,7 +12905,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>1188</v>
       </c>
@@ -12927,7 +12916,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="470" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>1188</v>
       </c>
@@ -12938,7 +12927,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="471" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1194</v>
       </c>
@@ -12949,7 +12938,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="472" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1197</v>
       </c>
@@ -12960,7 +12949,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="473" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1200</v>
       </c>
@@ -12971,7 +12960,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="474" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1203</v>
       </c>
@@ -12982,7 +12971,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="475" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1203</v>
       </c>
@@ -12993,7 +12982,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="476" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1207</v>
       </c>
@@ -13004,7 +12993,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="477" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1207</v>
       </c>
@@ -13015,7 +13004,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="478" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1207</v>
       </c>
@@ -13026,7 +13015,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1213</v>
       </c>
@@ -13037,7 +13026,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1216</v>
       </c>
@@ -13048,7 +13037,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="481" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>1218</v>
       </c>
@@ -13059,7 +13048,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="482" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1221</v>
       </c>
@@ -13070,7 +13059,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1221</v>
       </c>
@@ -13081,7 +13070,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="484" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>1226</v>
       </c>
@@ -13092,7 +13081,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="485" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1226</v>
       </c>
@@ -13103,7 +13092,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="486" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1226</v>
       </c>
@@ -13114,7 +13103,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="487" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1226</v>
       </c>
@@ -13125,7 +13114,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="488" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1233</v>
       </c>
@@ -13136,7 +13125,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1236</v>
       </c>
@@ -13147,7 +13136,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="490" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1238</v>
       </c>
@@ -13158,7 +13147,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="491" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1238</v>
       </c>
@@ -13169,7 +13158,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1242</v>
       </c>
@@ -13180,7 +13169,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="493" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1245</v>
       </c>
@@ -13191,7 +13180,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="494" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1245</v>
       </c>
@@ -13202,7 +13191,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="495" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>1249</v>
       </c>
@@ -13213,7 +13202,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="496" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1252</v>
       </c>
@@ -13224,7 +13213,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1255</v>
       </c>
@@ -13235,7 +13224,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1255</v>
       </c>
@@ -13246,7 +13235,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="499" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1258</v>
       </c>
@@ -13257,7 +13246,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1261</v>
       </c>
@@ -13268,7 +13257,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1264</v>
       </c>
@@ -13279,7 +13268,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="502" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1266</v>
       </c>
@@ -13290,7 +13279,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="503" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1266</v>
       </c>
@@ -13301,7 +13290,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1270</v>
       </c>
@@ -13312,7 +13301,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1272</v>
       </c>
@@ -13323,7 +13312,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="506" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1274</v>
       </c>
@@ -13334,7 +13323,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="507" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1274</v>
       </c>
@@ -13345,7 +13334,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="508" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1274</v>
       </c>
@@ -13356,7 +13345,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="509" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1279</v>
       </c>
@@ -13367,7 +13356,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="510" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1282</v>
       </c>
@@ -13378,7 +13367,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1282</v>
       </c>
@@ -13389,7 +13378,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="512" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1282</v>
       </c>
@@ -13400,7 +13389,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="513" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1282</v>
       </c>
@@ -13411,7 +13400,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="514" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1282</v>
       </c>
@@ -13422,7 +13411,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="515" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1291</v>
       </c>
@@ -13433,7 +13422,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="516" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1294</v>
       </c>
@@ -13444,7 +13433,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="517" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>1294</v>
       </c>
@@ -13455,7 +13444,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="518" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1298</v>
       </c>
@@ -13466,7 +13455,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1298</v>
       </c>
@@ -13477,7 +13466,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="520" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1298</v>
       </c>
@@ -13488,7 +13477,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="521" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1303</v>
       </c>
@@ -13499,7 +13488,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="522" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1303</v>
       </c>
@@ -13510,7 +13499,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1308</v>
       </c>
@@ -13521,7 +13510,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1311</v>
       </c>
@@ -13532,7 +13521,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1311</v>
       </c>
@@ -13543,7 +13532,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1315</v>
       </c>
@@ -13554,7 +13543,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1318</v>
       </c>
@@ -13565,7 +13554,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="528" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>1321</v>
       </c>
@@ -13576,7 +13565,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="529" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1324</v>
       </c>
@@ -13587,7 +13576,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="530" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1324</v>
       </c>
@@ -13598,7 +13587,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1327</v>
       </c>
@@ -13609,7 +13598,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="532" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1330</v>
       </c>
@@ -13620,7 +13609,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="533" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1333</v>
       </c>
@@ -13631,7 +13620,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="534" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1336</v>
       </c>
@@ -13642,7 +13631,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="535" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1336</v>
       </c>
@@ -13653,7 +13642,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="536" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1340</v>
       </c>
@@ -13664,7 +13653,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="537" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1343</v>
       </c>
@@ -13675,7 +13664,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="538" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1346</v>
       </c>
@@ -13686,7 +13675,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="539" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1349</v>
       </c>
@@ -13697,7 +13686,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1352</v>
       </c>
@@ -13708,7 +13697,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="541" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1355</v>
       </c>
@@ -13719,7 +13708,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="542" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1355</v>
       </c>
@@ -13730,7 +13719,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="543" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1359</v>
       </c>
@@ -13741,7 +13730,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="544" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1359</v>
       </c>
@@ -13752,7 +13741,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="545" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1363</v>
       </c>
@@ -13763,7 +13752,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="546" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1363</v>
       </c>
@@ -13774,7 +13763,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="547" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1367</v>
       </c>
@@ -13785,7 +13774,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="548" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1369</v>
       </c>
@@ -13796,7 +13785,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="549" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1369</v>
       </c>
@@ -13807,7 +13796,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1369</v>
       </c>
@@ -13818,7 +13807,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="551" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1375</v>
       </c>
@@ -13829,7 +13818,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="552" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1375</v>
       </c>
@@ -13840,7 +13829,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1379</v>
       </c>
@@ -13851,7 +13840,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="554" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>1382</v>
       </c>
@@ -13862,7 +13851,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="555" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1385</v>
       </c>
@@ -13873,7 +13862,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1385</v>
       </c>
@@ -13884,7 +13873,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="557" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1390</v>
       </c>
@@ -13895,7 +13884,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="558" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1393</v>
       </c>
@@ -13906,7 +13895,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="559" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1396</v>
       </c>
@@ -13917,7 +13906,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="560" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1396</v>
       </c>
@@ -13928,7 +13917,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="561" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1400</v>
       </c>
@@ -13939,7 +13928,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="562" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1403</v>
       </c>
@@ -13950,7 +13939,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="563" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1403</v>
       </c>
@@ -13961,7 +13950,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="564" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1407</v>
       </c>
@@ -13972,7 +13961,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1410</v>
       </c>
@@ -13983,7 +13972,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="566" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1413</v>
       </c>
@@ -13994,7 +13983,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="567" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1413</v>
       </c>
@@ -14005,7 +13994,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="568" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1418</v>
       </c>
@@ -14016,7 +14005,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1421</v>
       </c>
@@ -14027,7 +14016,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="570" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1423</v>
       </c>
@@ -14038,7 +14027,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1426</v>
       </c>
@@ -14049,7 +14038,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="572" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1429</v>
       </c>
@@ -14060,7 +14049,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1432</v>
       </c>
@@ -14082,7 +14071,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="575" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1434</v>
       </c>
@@ -14093,7 +14082,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="576" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1434</v>
       </c>
@@ -14104,7 +14093,7 @@
         <v>1439</v>
       </c>
     </row>
-    <row r="577" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1440</v>
       </c>
@@ -14115,7 +14104,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="578" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>1440</v>
       </c>
@@ -14126,7 +14115,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="579" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1444</v>
       </c>
@@ -14137,7 +14126,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="580" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1444</v>
       </c>
@@ -14148,7 +14137,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="581" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1448</v>
       </c>
@@ -14159,7 +14148,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="582" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1448</v>
       </c>
@@ -14170,7 +14159,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1452</v>
       </c>
@@ -14181,7 +14170,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="584" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1452</v>
       </c>
@@ -14192,7 +14181,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="585" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1457</v>
       </c>
@@ -14203,7 +14192,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="586" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1460</v>
       </c>
@@ -14214,7 +14203,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="587" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1462</v>
       </c>
@@ -14225,7 +14214,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1465</v>
       </c>
@@ -14236,7 +14225,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="589" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1467</v>
       </c>
@@ -14280,7 +14269,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="593" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1473</v>
       </c>
@@ -14302,7 +14291,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="595" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1476</v>
       </c>
@@ -14313,7 +14302,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="596" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>1476</v>
       </c>
@@ -14324,7 +14313,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="597" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1479</v>
       </c>
@@ -14335,7 +14324,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="598" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1481</v>
       </c>
@@ -14346,7 +14335,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="599" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1481</v>
       </c>
@@ -14357,7 +14346,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="600" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1481</v>
       </c>
@@ -14368,7 +14357,7 @@
         <v>1485</v>
       </c>
     </row>
-    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1487</v>
       </c>
@@ -14379,7 +14368,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="602" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>1489</v>
       </c>
@@ -14390,7 +14379,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="603" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1491</v>
       </c>
@@ -14401,7 +14390,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="604" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1493</v>
       </c>
@@ -14412,7 +14401,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="605" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1495</v>
       </c>
@@ -14423,7 +14412,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="606" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1498</v>
       </c>
@@ -14434,7 +14423,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="607" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1498</v>
       </c>
@@ -14445,7 +14434,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="608" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1498</v>
       </c>
@@ -14456,7 +14445,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="609" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1498</v>
       </c>
@@ -14467,7 +14456,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="610" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1498</v>
       </c>
@@ -14478,7 +14467,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="611" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1498</v>
       </c>
@@ -14489,7 +14478,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="612" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1507</v>
       </c>
@@ -14500,7 +14489,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="613" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1510</v>
       </c>
@@ -14511,7 +14500,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="614" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1513</v>
       </c>
@@ -14522,7 +14511,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="615" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1516</v>
       </c>
@@ -14533,7 +14522,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="616" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1516</v>
       </c>
@@ -14544,7 +14533,7 @@
         <v>1518</v>
       </c>
     </row>
-    <row r="617" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1520</v>
       </c>
@@ -14555,7 +14544,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="618" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1523</v>
       </c>
@@ -14566,7 +14555,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="619" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>1526</v>
       </c>
@@ -14577,7 +14566,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="620" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1526</v>
       </c>
@@ -14588,7 +14577,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="621" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1526</v>
       </c>
@@ -14599,7 +14588,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="622" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1526</v>
       </c>
@@ -14610,7 +14599,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="623" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1534</v>
       </c>
@@ -14621,7 +14610,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="624" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1537</v>
       </c>
@@ -14632,7 +14621,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="625" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1540</v>
       </c>
@@ -14643,7 +14632,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="626" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1540</v>
       </c>
@@ -14654,7 +14643,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="627" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1545</v>
       </c>
@@ -14665,7 +14654,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="628" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1548</v>
       </c>
@@ -14676,7 +14665,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="629" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1551</v>
       </c>
@@ -14687,7 +14676,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="630" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1551</v>
       </c>
@@ -14698,7 +14687,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="631" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1555</v>
       </c>
@@ -14709,7 +14698,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="632" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1555</v>
       </c>
@@ -14720,7 +14709,7 @@
         <v>1557</v>
       </c>
     </row>
-    <row r="633" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1559</v>
       </c>
@@ -14731,7 +14720,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="634" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1561</v>
       </c>
@@ -14742,7 +14731,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="635" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1561</v>
       </c>
@@ -14753,7 +14742,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="636" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1566</v>
       </c>
@@ -14764,7 +14753,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="637" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1568</v>
       </c>
@@ -14775,7 +14764,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="638" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1571</v>
       </c>
@@ -14786,7 +14775,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="639" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1571</v>
       </c>
@@ -14797,7 +14786,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="640" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1576</v>
       </c>
@@ -14808,7 +14797,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="641" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1576</v>
       </c>
@@ -14819,7 +14808,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="642" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1576</v>
       </c>
@@ -14830,7 +14819,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="643" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1576</v>
       </c>
@@ -14841,7 +14830,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="644" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1582</v>
       </c>
@@ -14852,7 +14841,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="645" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1584</v>
       </c>
@@ -14863,7 +14852,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="646" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1587</v>
       </c>
@@ -14874,7 +14863,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="647" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1587</v>
       </c>
@@ -14885,7 +14874,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="648" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1590</v>
       </c>
@@ -14896,7 +14885,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="649" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1593</v>
       </c>
@@ -14907,7 +14896,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="650" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1593</v>
       </c>
@@ -14918,7 +14907,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="651" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1597</v>
       </c>
@@ -14929,7 +14918,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="652" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1597</v>
       </c>
@@ -14940,7 +14929,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="653" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1601</v>
       </c>
@@ -14951,7 +14940,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="654" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1601</v>
       </c>
@@ -14962,7 +14951,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="655" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1605</v>
       </c>
@@ -14973,7 +14962,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="656" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1608</v>
       </c>
@@ -14984,7 +14973,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="657" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1611</v>
       </c>
@@ -14995,7 +14984,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="658" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1614</v>
       </c>
@@ -15006,7 +14995,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="659" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1614</v>
       </c>
@@ -15017,7 +15006,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="660" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1619</v>
       </c>
@@ -15028,7 +15017,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="661" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1619</v>
       </c>
@@ -15039,7 +15028,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="662" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1624</v>
       </c>
@@ -15050,7 +15039,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="663" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1624</v>
       </c>
@@ -15061,7 +15050,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="664" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1628</v>
       </c>
@@ -15072,7 +15061,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="665" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1628</v>
       </c>
@@ -15083,7 +15072,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="666" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>1631</v>
       </c>
@@ -15094,7 +15083,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="667" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>1634</v>
       </c>
@@ -15105,7 +15094,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="668" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>1634</v>
       </c>
@@ -15116,7 +15105,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="669" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>1638</v>
       </c>
@@ -15127,7 +15116,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="670" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>1641</v>
       </c>
@@ -15138,7 +15127,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="671" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>1644</v>
       </c>
@@ -15149,7 +15138,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="672" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>1647</v>
       </c>
@@ -15171,7 +15160,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="674" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>1650</v>
       </c>
@@ -15182,7 +15171,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="675" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>1654</v>
       </c>
@@ -15193,7 +15182,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="676" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>1657</v>
       </c>
@@ -15204,7 +15193,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="677" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>1657</v>
       </c>
@@ -15215,7 +15204,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="678" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>1657</v>
       </c>
@@ -15226,7 +15215,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="679" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>1657</v>
       </c>
@@ -15237,7 +15226,7 @@
         <v>1664</v>
       </c>
     </row>
-    <row r="680" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>1657</v>
       </c>
@@ -15259,7 +15248,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="682" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>1667</v>
       </c>
@@ -15270,7 +15259,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="683" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>1670</v>
       </c>
@@ -15281,7 +15270,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="684" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>1670</v>
       </c>
@@ -15292,7 +15281,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="685" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>1674</v>
       </c>
@@ -15303,7 +15292,7 @@
         <v>1676</v>
       </c>
     </row>
-    <row r="686" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>1677</v>
       </c>
@@ -15314,7 +15303,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="687" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>1680</v>
       </c>
@@ -15325,7 +15314,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="688" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>1683</v>
       </c>
@@ -15336,7 +15325,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="689" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>1683</v>
       </c>
@@ -15347,7 +15336,7 @@
         <v>1685</v>
       </c>
     </row>
-    <row r="690" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>1687</v>
       </c>
@@ -15358,7 +15347,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="691" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>1690</v>
       </c>
@@ -15369,7 +15358,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="692" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>1690</v>
       </c>
@@ -15380,7 +15369,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="693" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>1694</v>
       </c>
@@ -15391,7 +15380,7 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="694" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>1697</v>
       </c>
@@ -15402,7 +15391,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="695" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>1700</v>
       </c>
@@ -15413,7 +15402,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="696" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>1700</v>
       </c>
@@ -15424,7 +15413,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="697" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>1700</v>
       </c>
@@ -15435,7 +15424,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="698" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>1706</v>
       </c>
@@ -15446,7 +15435,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="699" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>1706</v>
       </c>
@@ -15457,7 +15446,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="700" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>1710</v>
       </c>
@@ -15468,7 +15457,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="701" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>1710</v>
       </c>
@@ -15479,7 +15468,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="702" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>1710</v>
       </c>
@@ -15490,7 +15479,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="703" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>1715</v>
       </c>
@@ -15501,7 +15490,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="704" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>1715</v>
       </c>
@@ -15512,7 +15501,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="705" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>1720</v>
       </c>
@@ -15523,7 +15512,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="706" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>1723</v>
       </c>
@@ -15534,7 +15523,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="707" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>1723</v>
       </c>
@@ -15545,7 +15534,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="708" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>1727</v>
       </c>
@@ -15556,7 +15545,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="709" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>1727</v>
       </c>
@@ -15567,7 +15556,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="710" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>1727</v>
       </c>
@@ -15578,7 +15567,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="711" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>1727</v>
       </c>
@@ -15589,7 +15578,7 @@
         <v>1734</v>
       </c>
     </row>
-    <row r="712" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>1735</v>
       </c>
@@ -15600,7 +15589,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="713" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>1735</v>
       </c>
@@ -15611,7 +15600,7 @@
         <v>1737</v>
       </c>
     </row>
-    <row r="714" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>1739</v>
       </c>
@@ -15622,7 +15611,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="715" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>1742</v>
       </c>
@@ -15633,7 +15622,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="716" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>1745</v>
       </c>
@@ -15644,7 +15633,7 @@
         <v>1747</v>
       </c>
     </row>
-    <row r="717" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>1748</v>
       </c>
@@ -15655,7 +15644,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="718" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>1748</v>
       </c>
@@ -15666,7 +15655,7 @@
         <v>1750</v>
       </c>
     </row>
-    <row r="719" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>1752</v>
       </c>
@@ -15677,7 +15666,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="720" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>1752</v>
       </c>
@@ -15688,7 +15677,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="721" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>1756</v>
       </c>
@@ -15699,7 +15688,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="722" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>1756</v>
       </c>
@@ -15710,7 +15699,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="723" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>1760</v>
       </c>
@@ -15721,7 +15710,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="724" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>1760</v>
       </c>
@@ -15732,7 +15721,7 @@
         <v>1762</v>
       </c>
     </row>
-    <row r="725" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>1764</v>
       </c>
@@ -15743,7 +15732,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="726" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>1764</v>
       </c>
@@ -15754,7 +15743,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="727" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>1768</v>
       </c>
@@ -15765,7 +15754,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="728" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>1770</v>
       </c>
@@ -15776,7 +15765,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="729" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>1770</v>
       </c>
@@ -15787,7 +15776,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="730" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>1770</v>
       </c>
@@ -15798,7 +15787,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="731" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>1776</v>
       </c>
@@ -15809,7 +15798,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="732" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>1776</v>
       </c>
@@ -15820,7 +15809,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="733" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>1776</v>
       </c>
@@ -15831,7 +15820,7 @@
         <v>1778</v>
       </c>
     </row>
-    <row r="734" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>1781</v>
       </c>
@@ -15842,7 +15831,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="735" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>1784</v>
       </c>
@@ -15853,7 +15842,7 @@
         <v>1786</v>
       </c>
     </row>
-    <row r="736" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>1787</v>
       </c>
@@ -15864,7 +15853,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="737" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>1787</v>
       </c>
@@ -15875,7 +15864,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="738" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>1791</v>
       </c>
@@ -15886,7 +15875,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="739" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>1793</v>
       </c>
@@ -15897,7 +15886,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="740" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>1796</v>
       </c>
@@ -15908,7 +15897,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="741" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>1799</v>
       </c>
@@ -15919,7 +15908,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="742" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>1802</v>
       </c>
@@ -15930,7 +15919,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="743" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>1805</v>
       </c>
@@ -15941,7 +15930,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="744" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>1805</v>
       </c>
@@ -15952,7 +15941,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="745" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>1810</v>
       </c>
@@ -15963,7 +15952,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="746" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>1810</v>
       </c>
@@ -15974,7 +15963,7 @@
         <v>1812</v>
       </c>
     </row>
-    <row r="747" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>1814</v>
       </c>
@@ -15985,7 +15974,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="748" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>1817</v>
       </c>
@@ -15996,7 +15985,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="749" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>1817</v>
       </c>
@@ -16007,7 +15996,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="750" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>1821</v>
       </c>
@@ -16018,7 +16007,7 @@
         <v>1823</v>
       </c>
     </row>
-    <row r="751" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>1821</v>
       </c>
@@ -16029,7 +16018,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="752" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>1821</v>
       </c>
@@ -16040,7 +16029,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="753" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>1821</v>
       </c>
@@ -16051,7 +16040,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="754" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>1821</v>
       </c>
@@ -16062,7 +16051,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="755" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>1830</v>
       </c>
@@ -16073,7 +16062,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="756" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>1830</v>
       </c>
@@ -16084,7 +16073,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="757" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>1830</v>
       </c>
@@ -16095,7 +16084,7 @@
         <v>1832</v>
       </c>
     </row>
-    <row r="758" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>1836</v>
       </c>
@@ -16106,7 +16095,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="759" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>1839</v>
       </c>
@@ -16117,7 +16106,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="760" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>1839</v>
       </c>
@@ -16128,7 +16117,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="761" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>1839</v>
       </c>
@@ -16139,7 +16128,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="762" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>1845</v>
       </c>
@@ -16150,7 +16139,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="763" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>1847</v>
       </c>
@@ -16161,7 +16150,7 @@
         <v>1849</v>
       </c>
     </row>
-    <row r="764" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>1847</v>
       </c>
@@ -16172,7 +16161,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="765" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>1847</v>
       </c>
@@ -16183,7 +16172,7 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="766" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>1854</v>
       </c>
@@ -16194,7 +16183,7 @@
         <v>1856</v>
       </c>
     </row>
-    <row r="767" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>1857</v>
       </c>
@@ -16205,7 +16194,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="768" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>1860</v>
       </c>
@@ -16216,7 +16205,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="769" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>1860</v>
       </c>
@@ -16227,7 +16216,7 @@
         <v>1864</v>
       </c>
     </row>
-    <row r="770" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>1865</v>
       </c>
@@ -16238,7 +16227,7 @@
         <v>1867</v>
       </c>
     </row>
-    <row r="771" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>1868</v>
       </c>
@@ -16249,7 +16238,7 @@
         <v>1859</v>
       </c>
     </row>
-    <row r="772" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>1870</v>
       </c>
@@ -16260,7 +16249,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="773" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>1873</v>
       </c>
@@ -16271,7 +16260,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="774" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>1873</v>
       </c>
@@ -16282,7 +16271,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="775" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>1873</v>
       </c>
@@ -16293,7 +16282,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="776" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>1878</v>
       </c>
@@ -16304,7 +16293,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="777" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>1881</v>
       </c>
@@ -16315,7 +16304,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="778" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>1881</v>
       </c>
@@ -16326,7 +16315,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="779" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>1885</v>
       </c>
@@ -16337,7 +16326,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="780" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>1885</v>
       </c>
@@ -16348,7 +16337,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="781" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>1885</v>
       </c>
@@ -16359,7 +16348,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="782" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>1891</v>
       </c>
@@ -16370,7 +16359,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="783" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>1891</v>
       </c>
@@ -16381,7 +16370,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="784" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>1895</v>
       </c>
@@ -16392,7 +16381,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="785" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>1898</v>
       </c>
@@ -16403,7 +16392,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="786" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>1901</v>
       </c>
@@ -16414,7 +16403,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="787" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>1904</v>
       </c>
@@ -16425,7 +16414,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="788" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>1907</v>
       </c>
@@ -16436,7 +16425,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="789" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="789" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>1907</v>
       </c>
@@ -16447,7 +16436,7 @@
         <v>1909</v>
       </c>
     </row>
-    <row r="790" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>1911</v>
       </c>
@@ -16458,7 +16447,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="791" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>1911</v>
       </c>
@@ -16469,7 +16458,7 @@
         <v>1913</v>
       </c>
     </row>
-    <row r="792" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="792" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>1915</v>
       </c>
@@ -16480,7 +16469,7 @@
         <v>1917</v>
       </c>
     </row>
-    <row r="793" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>1918</v>
       </c>
@@ -16491,7 +16480,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="794" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>1918</v>
       </c>
@@ -16502,7 +16491,7 @@
         <v>1920</v>
       </c>
     </row>
-    <row r="795" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>1922</v>
       </c>
@@ -16513,7 +16502,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="796" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>1924</v>
       </c>
@@ -16524,7 +16513,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="797" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>1926</v>
       </c>
@@ -16535,7 +16524,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="798" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>1928</v>
       </c>
@@ -16546,7 +16535,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="799" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>1931</v>
       </c>
@@ -16557,7 +16546,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="800" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>1931</v>
       </c>
@@ -16568,7 +16557,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="801" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>1935</v>
       </c>
@@ -16579,7 +16568,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="802" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>1935</v>
       </c>
@@ -16590,7 +16579,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="803" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>1935</v>
       </c>
@@ -16601,7 +16590,7 @@
         <v>1937</v>
       </c>
     </row>
-    <row r="804" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>1941</v>
       </c>
@@ -16612,7 +16601,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="805" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>1944</v>
       </c>
@@ -16623,7 +16612,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="806" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="806" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>1944</v>
       </c>
@@ -16634,7 +16623,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="807" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>1948</v>
       </c>
@@ -16645,7 +16634,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="808" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="808" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>1948</v>
       </c>
@@ -16656,7 +16645,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="809" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>1948</v>
       </c>
@@ -16667,7 +16656,7 @@
         <v>1950</v>
       </c>
     </row>
-    <row r="810" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>1953</v>
       </c>
@@ -16678,7 +16667,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="811" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>1953</v>
       </c>
@@ -16689,7 +16678,7 @@
         <v>1957</v>
       </c>
     </row>
-    <row r="812" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>1953</v>
       </c>
@@ -16700,7 +16689,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="813" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>1959</v>
       </c>
@@ -16711,7 +16700,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="814" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="814" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>1962</v>
       </c>
@@ -16722,7 +16711,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="815" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>1962</v>
       </c>
@@ -16733,7 +16722,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="816" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="816" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>1966</v>
       </c>
@@ -16744,7 +16733,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="817" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>1966</v>
       </c>
@@ -16755,7 +16744,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="818" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="818" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>1970</v>
       </c>
@@ -16766,7 +16755,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="819" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>1972</v>
       </c>
@@ -16777,7 +16766,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="820" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>1975</v>
       </c>
@@ -16788,7 +16777,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="821" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>1978</v>
       </c>
@@ -16799,7 +16788,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="822" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>1978</v>
       </c>
@@ -16810,7 +16799,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="823" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>1982</v>
       </c>
@@ -16821,7 +16810,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="824" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="824" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>1985</v>
       </c>
@@ -16832,7 +16821,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="825" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>1988</v>
       </c>
@@ -16843,7 +16832,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="826" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>1991</v>
       </c>
@@ -16854,7 +16843,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="827" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>1991</v>
       </c>
@@ -16865,7 +16854,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="828" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>1995</v>
       </c>
@@ -16876,7 +16865,7 @@
         <v>1997</v>
       </c>
     </row>
-    <row r="829" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>1998</v>
       </c>
@@ -16887,7 +16876,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="830" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>1998</v>
       </c>
@@ -16898,7 +16887,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="831" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>2002</v>
       </c>
@@ -16909,7 +16898,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="832" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>2005</v>
       </c>
@@ -16920,7 +16909,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="833" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>2008</v>
       </c>
@@ -16931,7 +16920,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="834" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="834" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>2008</v>
       </c>
@@ -16942,7 +16931,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="835" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="835" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>2013</v>
       </c>
@@ -16953,7 +16942,7 @@
         <v>2015</v>
       </c>
     </row>
-    <row r="836" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="836" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>2016</v>
       </c>
@@ -16964,7 +16953,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="837" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="837" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>2019</v>
       </c>
@@ -16975,7 +16964,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="838" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="838" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>2021</v>
       </c>
@@ -16986,7 +16975,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="839" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="839" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>2023</v>
       </c>
@@ -16997,7 +16986,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="840" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="840" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>2026</v>
       </c>
@@ -17008,7 +16997,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="841" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="841" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>2029</v>
       </c>
@@ -17019,7 +17008,7 @@
         <v>2031</v>
       </c>
     </row>
-    <row r="842" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="842" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>2032</v>
       </c>
@@ -17030,7 +17019,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="843" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="843" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>2032</v>
       </c>
@@ -17041,7 +17030,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="844" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="844" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>2036</v>
       </c>
@@ -17052,7 +17041,7 @@
         <v>2038</v>
       </c>
     </row>
-    <row r="845" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
+    <row r="845" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>2039</v>
       </c>
@@ -17063,7 +17052,7 @@
         <v>2041</v>
       </c>
     </row>
-    <row r="846" spans="1:3" ht="46.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="846" spans="1:3" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>2042</v>
       </c>
@@ -17074,7 +17063,7 @@
         <v>2044</v>
       </c>
     </row>
-    <row r="847" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="847" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>2045</v>
       </c>
@@ -17085,7 +17074,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="848" spans="1:3" ht="31.2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="848" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>2048</v>
       </c>
@@ -17096,7 +17085,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="849" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="849" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>2051</v>
       </c>
@@ -17107,7 +17096,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="850" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="850" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>2054</v>
       </c>
@@ -17129,7 +17118,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="852" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="852" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>2057</v>
       </c>
@@ -17151,7 +17140,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="854" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="854" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>2063</v>
       </c>
@@ -17162,7 +17151,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="855" spans="1:3" ht="78" hidden="1" x14ac:dyDescent="0.3">
+    <row r="855" spans="1:3" ht="78" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>2063</v>
       </c>
@@ -17173,7 +17162,7 @@
         <v>2065</v>
       </c>
     </row>
-    <row r="856" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="856" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>2067</v>
       </c>
@@ -17184,7 +17173,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="857" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="857" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>2070</v>
       </c>
@@ -17195,7 +17184,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="858" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="858" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>2073</v>
       </c>
@@ -17206,7 +17195,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="859" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="859" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>2076</v>
       </c>
@@ -17217,7 +17206,7 @@
         <v>2078</v>
       </c>
     </row>
-    <row r="860" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="860" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>2079</v>
       </c>
@@ -17228,7 +17217,7 @@
         <v>2081</v>
       </c>
     </row>
-    <row r="861" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="861" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>2082</v>
       </c>
@@ -17239,7 +17228,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="862" spans="1:3" ht="62.4" hidden="1" x14ac:dyDescent="0.3">
+    <row r="862" spans="1:3" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>2085</v>
       </c>
@@ -17262,16 +17251,12 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C863" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:C863" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
